--- a/Project/outputs/tables/table_war_vs_calm.xlsx
+++ b/Project/outputs/tables/table_war_vs_calm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,50 +436,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>A: Pure Calm Mean</t>
+          <t>A: Pure Calm</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>B: War-Only Mean</t>
+          <t>B: War Only</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>C: Crisis-Only Mean</t>
+          <t>C: Crisis Only</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>D: War+Crisis Mean</t>
+          <t>D: War+Crisis</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>High-Int Mean</t>
+          <t>B/A Ratio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>B/A Ratio</t>
+          <t>C/A Ratio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>C/A Ratio</t>
+          <t>t-stat (B vs A)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>t-stat (B vs A)</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Significant?</t>
         </is>
@@ -492,33 +487,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1531</v>
+        <v>0.1505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1386</v>
+        <v>0.1235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.462</v>
+        <v>0.3995</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3293</v>
+        <v>0.3574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1431</v>
+        <v>0.821</v>
       </c>
       <c r="G2" t="n">
-        <v>0.905</v>
+        <v>2.655</v>
       </c>
       <c r="H2" t="n">
-        <v>3.018</v>
+        <v>-7.29</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.429</v>
-      </c>
-      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -527,115 +519,106 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1636</v>
+        <v>0.1875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1383</v>
+        <v>0.184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3919</v>
+        <v>0.3797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2841</v>
+        <v>0.3095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1174</v>
+        <v>0.981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.845</v>
+        <v>2.025</v>
       </c>
       <c r="H3" t="n">
-        <v>2.395</v>
+        <v>-0.452</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.959</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>✅</t>
+        <v>0.6513</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1629</v>
+        <v>0.182</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1289</v>
+        <v>0.1797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3927</v>
+        <v>0.3807</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2969</v>
+        <v>0.3474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1055</v>
+        <v>0.987</v>
       </c>
       <c r="G4" t="n">
-        <v>0.791</v>
+        <v>2.091</v>
       </c>
       <c r="H4" t="n">
-        <v>2.41</v>
+        <v>-0.339</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.878</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>✅</t>
+        <v>0.7346</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1744</v>
+        <v>0.1442</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1691</v>
+        <v>0.1315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4202</v>
+        <v>0.349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3308</v>
+        <v>0.2799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1437</v>
+        <v>0.912</v>
       </c>
       <c r="G5" t="n">
-        <v>0.97</v>
+        <v>2.421</v>
       </c>
       <c r="H5" t="n">
-        <v>2.41</v>
+        <v>-2.517</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.247</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="K5" t="inlineStr">
+        <v>0.0124</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -648,33 +631,30 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2028</v>
+        <v>0.198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1901</v>
+        <v>0.1845</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4511</v>
+        <v>0.3635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2714</v>
+        <v>0.3849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2186</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.836</v>
       </c>
       <c r="H6" t="n">
-        <v>2.225</v>
+        <v>-3.555</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.809</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
+        <v>0.0004</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -683,37 +663,34 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2206</v>
+        <v>0.1884</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1905</v>
+        <v>0.1613</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5039</v>
+        <v>0.3491</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2665</v>
+        <v>0.3736</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2291</v>
+        <v>0.856</v>
       </c>
       <c r="G7" t="n">
-        <v>0.863</v>
+        <v>1.853</v>
       </c>
       <c r="H7" t="n">
-        <v>2.284</v>
+        <v>-4.185</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.115</v>
-      </c>
-      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -722,37 +699,34 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3185</v>
+        <v>0.1984</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1881</v>
+        <v>0.1601</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3857</v>
+        <v>0.3867</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2389</v>
+        <v>0.4541</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1558</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.591</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
-        <v>1.211</v>
+        <v>-11.507</v>
       </c>
       <c r="I8" t="n">
-        <v>-27.828</v>
-      </c>
-      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -761,37 +735,34 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2715</v>
+        <v>0.1977</v>
       </c>
       <c r="C9" t="n">
-        <v>0.186</v>
+        <v>0.1396</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7341</v>
+        <v>0.2818</v>
       </c>
       <c r="E9" t="n">
-        <v>0.355</v>
+        <v>0.3314</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1746</v>
+        <v>0.706</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.426</v>
       </c>
       <c r="H9" t="n">
-        <v>2.704</v>
+        <v>-15.374</v>
       </c>
       <c r="I9" t="n">
-        <v>-26.852</v>
-      </c>
-      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
